--- a/Day 3/Guerrilla AI - Day 3 - Demo Start.xlsx
+++ b/Day 3/Guerrilla AI - Day 3 - Demo Start.xlsx
@@ -559,7 +559,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Follow the numbered steps below live with George. Everything happens in this workbook. Nothing to install, nothing to license.</t>
+          <t xml:space="preserve">Watch live. Reply in chat with a word or letter when invited. Try the workbook afterward at your own pace.</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <row r="6" ht="21" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Six recorded steps, no formulas, no code.</t>
+          <t xml:space="preserve">Which removes extra spaces? A = Trim; B = Split. Reply in chat or think of your choice.</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
     <row r="11" ht="21" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>New month, one click.</t>
+          <t xml:space="preserve">The next month arrives. What do we do? REDO / REFRESH. Reply in chat or think of your choice.</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t># The applause line
+          <t># Replay the saved cleanup
 1. Copy the June rows from the june-rows sheet
 2. Paste them at the bottom of RawExport
 3. Right-click the SalesClean table &gt; Refresh
@@ -631,14 +631,14 @@
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>✓  Takeaway</t>
+          <t xml:space="preserve">One small next step</t>
         </is>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>One hour of Power Query replaces a recurring cleanup chore forever.</t>
+          <t xml:space="preserve">Pick one cleanup to save: SPACES, SPLIT, or TYPES. Record that step in Power Query, then try Refresh.</t>
         </is>
       </c>
     </row>
